--- a/data/trans_orig/P21D_5_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P21D_5_R-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitando atención sanitaria psiquiátrica, no la pudo recibir por motivos económicos en 2023</t>
+          <t>Población que, necesitando atención sanitaria psiquiátrica, no la pudo recibir por motivos económicos en 2023 (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -735,7 +735,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5333</t>
+          <t>5392</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>368</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>5423</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>703</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7563</t>
+          <t>7275</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>225544</t>
+          <t>225485</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>330510</t>
+          <t>330570</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>335628</t>
+          <t>335625</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>559307</t>
+          <t>559595</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>566127</t>
+          <t>566167</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>99,88%</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>4414</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8067</t>
+          <t>7785</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1595</t>
+          <t>1643</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8972</t>
+          <t>10226</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,5%</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1113440</t>
+          <t>1112555</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>929246</t>
+          <t>929528</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>936025</t>
+          <t>936042</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2045310</t>
+          <t>2044056</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2052687</t>
+          <t>2052639</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5693</t>
+          <t>6147</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3381</t>
+          <t>3306</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6958</t>
+          <t>7640</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>304490</t>
+          <t>304036</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>308906</t>
+          <t>308981</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>615513</t>
+          <t>614831</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>979</t>
+          <t>1012</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8657</t>
+          <t>9885</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2771</t>
+          <t>2867</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10979</t>
+          <t>11139</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4492</t>
+          <t>4798</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15561</t>
+          <t>15838</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,49%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1649373</t>
+          <t>1648145</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1657051</t>
+          <t>1657018</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1574614</t>
+          <t>1574454</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1582822</t>
+          <t>1582726</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3228062</t>
+          <t>3227785</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3239131</t>
+          <t>3238825</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,85%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P21D_5_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P21D_5_R-Estudios-trans_orig.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>995</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5392</t>
+          <t>4701</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,22 +760,22 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1791</t>
+          <t>1898</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>388</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5423</t>
+          <t>5748</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>2795</t>
+          <t>2893</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>703</t>
+          <t>802</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7275</t>
+          <t>7584</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -838,27 +838,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>229873</t>
+          <t>252660</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>225485</t>
+          <t>248954</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>230877</t>
+          <t>253655</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -873,27 +873,27 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>334202</t>
+          <t>359907</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>330570</t>
+          <t>356057</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>335625</t>
+          <t>361417</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>564075</t>
+          <t>612567</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>559595</t>
+          <t>607876</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>566167</t>
+          <t>614658</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,88%</t>
+          <t>99,87%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>230877</t>
+          <t>253655</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>230877</t>
+          <t>253655</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>230877</t>
+          <t>253655</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>335993</t>
+          <t>361805</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>335993</t>
+          <t>361805</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>335993</t>
+          <t>361805</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>566870</t>
+          <t>615460</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>566870</t>
+          <t>615460</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>566870</t>
+          <t>615460</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>660</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1078,12 +1078,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4414</t>
+          <t>3262</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3496</t>
+          <t>4089</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1660</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7785</t>
+          <t>8654</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,27 +1138,27 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>4189</t>
+          <t>4748</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1643</t>
+          <t>1896</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10226</t>
+          <t>9708</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1181,27 +1181,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1116276</t>
+          <t>957694</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1112555</t>
+          <t>955092</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1116969</t>
+          <t>958354</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>99,94%</t>
+          <t>99,93%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>933817</t>
+          <t>981430</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>929528</t>
+          <t>976865</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>936042</t>
+          <t>983859</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,22 +1251,22 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2050093</t>
+          <t>1939125</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2044056</t>
+          <t>1934165</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2052639</t>
+          <t>1941977</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,76%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,92%</t>
+          <t>99,9%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1116969</t>
+          <t>958354</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1116969</t>
+          <t>958354</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1116969</t>
+          <t>958354</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>937313</t>
+          <t>985519</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>937313</t>
+          <t>985519</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>937313</t>
+          <t>985519</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2054282</t>
+          <t>1943873</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2054282</t>
+          <t>1943873</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2054282</t>
+          <t>1943873</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1684</t>
+          <t>1731</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1421,12 +1421,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>7616</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>692</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1456,12 +1456,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3306</t>
+          <t>3378</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,22 +1481,22 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>2335</t>
+          <t>2423</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>573</t>
+          <t>591</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7640</t>
+          <t>6596</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>0,96%</t>
         </is>
       </c>
     </row>
@@ -1524,27 +1524,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>308499</t>
+          <t>345478</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>304036</t>
+          <t>339593</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>310183</t>
+          <t>347209</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1559,27 +1559,27 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>311636</t>
+          <t>341548</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>308981</t>
+          <t>338862</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>312287</t>
+          <t>342240</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,8%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1594,27 +1594,27 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>620136</t>
+          <t>687025</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>614831</t>
+          <t>682852</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>621898</t>
+          <t>688857</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>310183</t>
+          <t>347209</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>310183</t>
+          <t>347209</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>310183</t>
+          <t>347209</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>312287</t>
+          <t>342240</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>312287</t>
+          <t>342240</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>312287</t>
+          <t>342240</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>622471</t>
+          <t>689448</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>622471</t>
+          <t>689448</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>622471</t>
+          <t>689448</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,67 +1754,67 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3381</t>
+          <t>3385</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1012</t>
+          <t>993</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9885</t>
+          <t>8771</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,06%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>0,56%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>6679</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>3306</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>12529</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
           <t>0,2%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,06%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>5938</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>2867</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>11139</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>9319</t>
+          <t>10064</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4798</t>
+          <t>5632</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15838</t>
+          <t>16318</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,5%</t>
         </is>
       </c>
     </row>
@@ -1867,69 +1867,69 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1654649</t>
+          <t>1555833</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1648145</t>
+          <t>1550447</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1657018</t>
+          <t>1558225</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
+          <t>99,78%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>99,44%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,94%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>2354</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>1682884</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>1677034</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>1686257</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>99,6%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>99,26%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
           <t>99,8%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>99,4%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>99,94%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>2354</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>1579655</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>1574454</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>1582726</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,63%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>99,3%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,82%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>3801</t>
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>3234304</t>
+          <t>3238717</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3227785</t>
+          <t>3232463</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3238825</t>
+          <t>3243149</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,83%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1658030</t>
+          <t>1559218</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1658030</t>
+          <t>1559218</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1658030</t>
+          <t>1559218</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1585593</t>
+          <t>1689563</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1585593</t>
+          <t>1689563</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1585593</t>
+          <t>1689563</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>3243623</t>
+          <t>3248781</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>3243623</t>
+          <t>3248781</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>3243623</t>
+          <t>3248781</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
